--- a/data/processed/positivacao/2023-03_positivacao_anonimizado.xlsx
+++ b/data/processed/positivacao/2023-03_positivacao_anonimizado.xlsx
@@ -551,7 +551,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Vendedor: 1 - ROBSON</t>
+          <t>Vendedor: 1 - VENDEDOR 01</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
@@ -26193,7 +26193,7 @@
     <row r="995">
       <c r="A995" t="inlineStr">
         <is>
-          <t>Vendedor: 3 - FERNANDA</t>
+          <t>Vendedor: 3 - VENDEDOR 03</t>
         </is>
       </c>
       <c r="B995" t="inlineStr"/>
@@ -37675,7 +37675,7 @@
     <row r="1437">
       <c r="A1437" t="inlineStr">
         <is>
-          <t>Vendedor: 4 - DANIELA</t>
+          <t>Vendedor: 4 - VENDEDOR 04</t>
         </is>
       </c>
       <c r="B1437" t="inlineStr"/>
@@ -66541,7 +66541,7 @@
     <row r="2548">
       <c r="A2548" t="inlineStr">
         <is>
-          <t>Vendedor: 8 - RAFAEL</t>
+          <t>Vendedor: 8 - VENDEDOR 08</t>
         </is>
       </c>
       <c r="B2548" t="inlineStr"/>
@@ -68160,12 +68160,12 @@
       <c r="A2611" t="inlineStr"/>
       <c r="B2611" t="inlineStr">
         <is>
-          <t>Vendedor 1 - ROBSON: positivou 7 cliente(s), não positivou 89 cliente(s) - Total vendido: R$ 14.110,44
+          <t>Vendedor 1 - VENDEDOR 01: positivou 7 cliente(s), não positivou 89 cliente(s) - Total vendido: R$ 14.110,44
 Vendedor 18 - LOJA: positivou 173 cliente(s), não positivou 716 cliente(s) - Total vendido: R$ 85.553,72
-Vendedor 3 - FERNANDA: positivou 121 cliente(s), não positivou 320 cliente(s) - Total vendido: R$ 181.906,45
-Vendedor 4 - DANIELA: positivou 84 cliente(s), não positivou 584 cliente(s) - Total vendido: R$ 48.736,48
+Vendedor 3 - VENDEDOR 03: positivou 121 cliente(s), não positivou 320 cliente(s) - Total vendido: R$ 181.906,45
+Vendedor 4 - VENDEDOR 04: positivou 84 cliente(s), não positivou 584 cliente(s) - Total vendido: R$ 48.736,48
 Vendedor 5 - SITE: positivou 14 cliente(s), não positivou 427 cliente(s) - Total vendido: R$ 2.649,55
-Vendedor 8 - RAFAEL: positivou 0 cliente(s), não positivou 61 cliente(s) - Total vendido: R$ 0,00</t>
+Vendedor 8 - VENDEDOR 08: positivou 0 cliente(s), não positivou 61 cliente(s) - Total vendido: R$ 0,00</t>
         </is>
       </c>
       <c r="C2611" t="inlineStr"/>
